--- a/data/trans_dic/P14B23-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,84</t>
+          <t>1,62; 6,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,43</t>
+          <t>1,18; 5,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,44</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,12</t>
+          <t>6,19; 13,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,99</t>
+          <t>7,26; 15,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,33</t>
+          <t>3,05; 6,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,42</t>
+          <t>4,38; 8,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,09</t>
+          <t>4,62; 9,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,25</t>
+          <t>2,06; 4,13</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,85</t>
+          <t>1,65; 5,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,51</t>
+          <t>1,5; 4,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,08</t>
+          <t>2,39; 6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,37</t>
+          <t>7,93; 13,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 11,19</t>
+          <t>6,16; 11,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 12,95</t>
+          <t>8,61; 12,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,72</t>
+          <t>5,3; 8,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,38</t>
+          <t>4,32; 7,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 9,03</t>
+          <t>5,97; 8,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,36</t>
+          <t>1,51; 5,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,38</t>
+          <t>0,29; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,93</t>
+          <t>3,77; 8,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 9,71</t>
+          <t>4,01; 9,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,25</t>
+          <t>3,3; 8,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,87</t>
+          <t>4,6; 8,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,51</t>
+          <t>3,22; 6,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,98</t>
+          <t>2,01; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,89</t>
+          <t>4,51; 7,74</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,95</t>
+          <t>0,52; 3,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,05</t>
+          <t>2,82; 8,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,69</t>
+          <t>6,19; 12,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,2</t>
+          <t>2,81; 7,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,9</t>
+          <t>4,12; 9,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,34</t>
+          <t>3,03; 6,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,56</t>
+          <t>2,06; 4,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,28</t>
+          <t>4,47; 8,2</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,68</t>
+          <t>1,43; 7,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,88</t>
+          <t>2,69; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,24</t>
+          <t>0,33; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 21,92</t>
+          <t>11,79; 21,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,47</t>
+          <t>4,87; 12,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,56</t>
+          <t>1,84; 5,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,89</t>
+          <t>7,34; 13,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,25</t>
+          <t>4,64; 9,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,95</t>
+          <t>1,65; 3,92</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,25</t>
+          <t>1,48; 6,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,6</t>
+          <t>0,3; 2,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,55</t>
+          <t>3,56; 8,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,11</t>
+          <t>5,84; 12,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 13,98</t>
+          <t>6,64; 13,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,95</t>
+          <t>5,01; 9,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,14</t>
+          <t>4,05; 8,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,73</t>
+          <t>3,65; 7,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,37</t>
+          <t>4,63; 8,12</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,14</t>
+          <t>1,49; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,43</t>
+          <t>0,48; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,12</t>
+          <t>3,22; 7,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,06</t>
+          <t>4,04; 7,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,13</t>
+          <t>2,82; 6,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,01</t>
+          <t>3,65; 11,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,42</t>
+          <t>3,21; 5,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,83</t>
+          <t>1,81; 3,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,27</t>
+          <t>4,17; 8,35</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,35</t>
+          <t>1,05; 3,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,38</t>
+          <t>1,23; 3,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,05</t>
+          <t>0,78; 3,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,87</t>
+          <t>4,51; 8,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,25</t>
+          <t>4,94; 8,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,65</t>
+          <t>5,62; 8,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,3</t>
+          <t>3,13; 5,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,44</t>
+          <t>3,33; 5,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,33</t>
+          <t>2,59; 5,37</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,15</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,52; 2,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,42</t>
+          <t>2,76; 4,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,13; 9,01</t>
+          <t>7,1; 8,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,57</t>
+          <t>5,83; 7,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,09</t>
+          <t>5,86; 8,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,83</t>
+          <t>4,83; 5,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,91</t>
+          <t>3,94; 4,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,09</t>
+          <t>4,81; 6,15</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4684; 17226</t>
+          <t>4779; 17768</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3332; 15953</t>
+          <t>3462; 16019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1670; 10714</t>
+          <t>1671; 9871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16741; 37555</t>
+          <t>17707; 37418</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21090; 43287</t>
+          <t>20971; 44933</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8648; 18338</t>
+          <t>8840; 18361</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25161; 48935</t>
+          <t>25456; 49231</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27074; 52923</t>
+          <t>26907; 53167</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11996; 25559</t>
+          <t>12402; 24805</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8813; 29570</t>
+          <t>8346; 29744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7310; 22676</t>
+          <t>7544; 22828</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12257; 31521</t>
+          <t>12415; 32614</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40478; 70024</t>
+          <t>41515; 69992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31606; 58557</t>
+          <t>32204; 58542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44310; 66704</t>
+          <t>44356; 66636</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54768; 89804</t>
+          <t>54596; 90532</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44442; 75685</t>
+          <t>44352; 74340</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61517; 93328</t>
+          <t>61654; 92769</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4864; 17354</t>
+          <t>4898; 16663</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>933; 7586</t>
+          <t>934; 7621</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11271; 28215</t>
+          <t>11913; 28170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13766; 33029</t>
+          <t>13641; 30937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11323; 27747</t>
+          <t>11092; 27648</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16436; 30954</t>
+          <t>16069; 28976</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21854; 43237</t>
+          <t>21368; 44465</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13611; 32606</t>
+          <t>13143; 31405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30871; 52477</t>
+          <t>30024; 51513</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7521</t>
+          <t>0; 7206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1083; 10930</t>
+          <t>1935; 11272</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9597; 28291</t>
+          <t>8801; 25896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23241; 45026</t>
+          <t>23834; 46636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10930; 27868</t>
+          <t>10873; 27488</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18654; 47074</t>
+          <t>19619; 46682</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24530; 48136</t>
+          <t>23032; 48061</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14739; 34563</t>
+          <t>15622; 34208</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34288; 65247</t>
+          <t>35259; 64637</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3029; 14203</t>
+          <t>3045; 15117</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5618; 18767</t>
+          <t>5685; 17906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>648; 5794</t>
+          <t>590; 5346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25595; 48142</t>
+          <t>25886; 47397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11400; 27247</t>
+          <t>10650; 26778</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4589; 14394</t>
+          <t>4752; 14692</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31110; 55713</t>
+          <t>31719; 57268</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20489; 39739</t>
+          <t>19961; 39502</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7119; 17273</t>
+          <t>7200; 17158</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4299; 17123</t>
+          <t>4052; 16618</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>789; 6850</t>
+          <t>791; 7308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9427; 23045</t>
+          <t>9602; 22329</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15396; 33664</t>
+          <t>16243; 34932</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18689; 38195</t>
+          <t>18132; 37781</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12879; 25583</t>
+          <t>12877; 24967</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22808; 44919</t>
+          <t>22342; 44403</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20355; 41474</t>
+          <t>19563; 41434</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25028; 44074</t>
+          <t>24408; 42753</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9798; 27456</t>
+          <t>9900; 26882</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2751; 15934</t>
+          <t>3126; 16483</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20485; 44456</t>
+          <t>20084; 44385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29072; 55848</t>
+          <t>28021; 53924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19337; 42369</t>
+          <t>19522; 42095</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30669; 93471</t>
+          <t>31012; 95039</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42983; 73493</t>
+          <t>43581; 73887</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24671; 51598</t>
+          <t>24435; 50832</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>56890; 121928</t>
+          <t>61420; 122980</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8232; 26060</t>
+          <t>8177; 24533</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10536; 26311</t>
+          <t>9594; 25969</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6680; 28355</t>
+          <t>7245; 30307</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37491; 64618</t>
+          <t>37060; 66017</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>39331; 68167</t>
+          <t>40778; 70539</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39554; 62088</t>
+          <t>40353; 62282</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49990; 84656</t>
+          <t>49997; 81122</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>54099; 87243</t>
+          <t>53389; 88287</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41964; 87685</t>
+          <t>42618; 88368</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>68163; 107992</t>
+          <t>67656; 107473</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53009; 85211</t>
+          <t>51745; 84366</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97311; 153069</t>
+          <t>95568; 151131</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>253008; 319642</t>
+          <t>251793; 317833</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>208193; 268155</t>
+          <t>206790; 268244</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>214393; 300328</t>
+          <t>217540; 301198</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>333642; 406157</t>
+          <t>336930; 414637</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>270864; 340407</t>
+          <t>273416; 340593</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>344408; 437020</t>
+          <t>345309; 440752</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P14B23-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P14B23-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,03</t>
+          <t>1,47; 5,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,45</t>
+          <t>1,03; 5,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,17</t>
+          <t>0,51; 3,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 13,08</t>
+          <t>6,1; 12,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,56</t>
+          <t>7,51; 15,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,34</t>
+          <t>3,04; 6,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,48</t>
+          <t>4,36; 8,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,13</t>
+          <t>4,68; 9,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,13</t>
+          <t>2,04; 4,1</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,88</t>
+          <t>1,62; 5,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,54</t>
+          <t>1,48; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,29</t>
+          <t>2,49; 6,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,36</t>
+          <t>7,89; 13,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,19</t>
+          <t>6,07; 11,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,94</t>
+          <t>8,81; 13,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,8</t>
+          <t>5,26; 8,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,25</t>
+          <t>4,3; 7,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,98</t>
+          <t>6,13; 9,15</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,14</t>
+          <t>1,76; 5,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,39</t>
+          <t>0,29; 2,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,91</t>
+          <t>3,43; 8,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,1</t>
+          <t>4,12; 10,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,22</t>
+          <t>3,2; 8,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,3</t>
+          <t>4,81; 9,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,7</t>
+          <t>3,29; 6,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,8</t>
+          <t>2,12; 5,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,74</t>
+          <t>4,75; 7,85</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,05</t>
+          <t>0,5; 2,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,29</t>
+          <t>2,66; 7,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,11</t>
+          <t>5,93; 11,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,1</t>
+          <t>2,74; 7,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,81</t>
+          <t>6,57; 11,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 6,33</t>
+          <t>3,34; 6,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,52</t>
+          <t>2,07; 4,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,2</t>
+          <t>5,34; 8,66</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 7,11</t>
+          <t>1,49; 6,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 8,48</t>
+          <t>2,35; 8,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,99</t>
+          <t>0,27; 2,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,79; 21,58</t>
+          <t>11,73; 21,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 12,25</t>
+          <t>5,27; 12,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,68</t>
+          <t>2,88; 6,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 13,25</t>
+          <t>7,21; 12,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,19</t>
+          <t>4,63; 9,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,92</t>
+          <t>1,89; 4,15</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,07</t>
+          <t>1,51; 6,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,78</t>
+          <t>0,3; 2,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,28</t>
+          <t>3,38; 8,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,56</t>
+          <t>5,59; 12,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 13,83</t>
+          <t>6,39; 13,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,71</t>
+          <t>4,83; 9,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 8,04</t>
+          <t>4,19; 8,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,73</t>
+          <t>3,6; 7,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,12</t>
+          <t>4,7; 7,96</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,06</t>
+          <t>1,52; 4,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,51</t>
+          <t>0,45; 2,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,11</t>
+          <t>3,27; 7,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,78</t>
+          <t>4,18; 7,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,09</t>
+          <t>2,81; 6,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 11,19</t>
+          <t>8,57; 12,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,45</t>
+          <t>3,18; 5,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,77</t>
+          <t>1,89; 3,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,35</t>
+          <t>6,41; 9,24</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,16</t>
+          <t>1,05; 3,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,34</t>
+          <t>1,35; 3,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,26</t>
+          <t>1,73; 4,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,04</t>
+          <t>4,57; 7,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,54</t>
+          <t>4,78; 8,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,68</t>
+          <t>5,57; 8,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,08</t>
+          <t>3,18; 5,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,5</t>
+          <t>3,37; 5,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,37</t>
+          <t>4,01; 5,84</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,02; 3,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,49</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,37</t>
+          <t>3,14; 4,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,96</t>
+          <t>7,19; 8,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,57</t>
+          <t>5,87; 7,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,11</t>
+          <t>7,28; 8,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,95</t>
+          <t>4,79; 5,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,94; 4,91</t>
+          <t>3,92; 4,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,15</t>
+          <t>5,43; 6,47</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18264</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4779; 17768</t>
+          <t>4321; 17230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3462; 16019</t>
+          <t>3025; 14842</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1671; 9871</t>
+          <t>1628; 9630</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17707; 37418</t>
+          <t>17450; 37013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20971; 44933</t>
+          <t>21669; 43755</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8840; 18361</t>
+          <t>9602; 20323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25456; 49231</t>
+          <t>25309; 48544</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26907; 53167</t>
+          <t>27245; 56300</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12402; 24805</t>
+          <t>12935; 26009</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>58995</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>75570</t>
+          <t>80293</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8346; 29744</t>
+          <t>8166; 28711</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7544; 22828</t>
+          <t>7441; 22331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12415; 32614</t>
+          <t>13196; 32355</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41515; 69992</t>
+          <t>41308; 70721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32204; 58542</t>
+          <t>31751; 58643</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44356; 66636</t>
+          <t>48133; 72438</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54596; 90532</t>
+          <t>54149; 90109</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44352; 74340</t>
+          <t>44130; 75601</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61654; 92769</t>
+          <t>66031; 98538</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>41133</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4898; 16663</t>
+          <t>5690; 17789</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>934; 7621</t>
+          <t>933; 7785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11913; 28170</t>
+          <t>10841; 26850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13641; 30937</t>
+          <t>14003; 34050</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11092; 27648</t>
+          <t>10772; 28457</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16069; 28976</t>
+          <t>17129; 32077</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21368; 44465</t>
+          <t>21868; 42397</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13143; 31405</t>
+          <t>13888; 33168</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30024; 51513</t>
+          <t>31953; 52777</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33609</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>53620</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7206</t>
+          <t>0; 6674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1935; 11272</t>
+          <t>1849; 10881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8801; 25896</t>
+          <t>9940; 29715</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23834; 46636</t>
+          <t>22847; 45718</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10873; 27488</t>
+          <t>10611; 27381</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19619; 46682</t>
+          <t>27724; 47040</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23032; 48061</t>
+          <t>25323; 49002</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15622; 34208</t>
+          <t>15647; 34216</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35259; 64637</t>
+          <t>42441; 68869</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>12240</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3045; 15117</t>
+          <t>3159; 14084</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5685; 17906</t>
+          <t>4964; 17358</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>590; 5346</t>
+          <t>545; 5783</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25886; 47397</t>
+          <t>25761; 47598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10650; 26778</t>
+          <t>11516; 27283</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4752; 14692</t>
+          <t>6597; 14518</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31719; 57268</t>
+          <t>31154; 55476</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19961; 39502</t>
+          <t>19914; 39599</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7200; 17158</t>
+          <t>8192; 18035</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>18560</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>33024</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4052; 16618</t>
+          <t>4124; 16974</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>791; 7308</t>
+          <t>795; 7446</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9602; 22329</t>
+          <t>9142; 21942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16243; 34932</t>
+          <t>15534; 34350</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18132; 37781</t>
+          <t>17463; 37488</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12877; 24967</t>
+          <t>12737; 25712</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22342; 44403</t>
+          <t>23155; 45466</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19563; 41434</t>
+          <t>19279; 42721</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24408; 42753</t>
+          <t>25112; 42560</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30309</t>
+          <t>35675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66943</t>
+          <t>80759</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>97252</t>
+          <t>116434</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9900; 26882</t>
+          <t>10071; 28612</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3126; 16483</t>
+          <t>2949; 15473</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20084; 44385</t>
+          <t>23526; 51435</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28021; 53924</t>
+          <t>28975; 53395</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19522; 42095</t>
+          <t>19449; 42355</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31012; 95039</t>
+          <t>66196; 97182</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43581; 73887</t>
+          <t>43119; 73582</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24435; 50832</t>
+          <t>25430; 51983</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61420; 122980</t>
+          <t>95557; 137870</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>57844</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>68600</t>
+          <t>79540</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>8177; 24533</t>
+          <t>8189; 24409</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9594; 25969</t>
+          <t>10478; 26659</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7245; 30307</t>
+          <t>13829; 32167</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37060; 66017</t>
+          <t>37580; 65440</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>40778; 70539</t>
+          <t>39485; 69036</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40353; 62282</t>
+          <t>46334; 71233</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49997; 81122</t>
+          <t>50784; 85540</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>53389; 88287</t>
+          <t>54091; 88516</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42618; 88368</t>
+          <t>65337; 95119</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125802</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>268431</t>
+          <t>299330</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>394233</t>
+          <t>434548</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>67656; 107473</t>
+          <t>69133; 108333</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>51745; 84366</t>
+          <t>51778; 86034</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>95568; 151131</t>
+          <t>110878; 160747</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>251793; 317833</t>
+          <t>255069; 317908</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>206790; 268244</t>
+          <t>207921; 270549</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>217540; 301198</t>
+          <t>272183; 328950</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>336930; 414637</t>
+          <t>334280; 407596</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>273416; 340593</t>
+          <t>271816; 345097</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>345309; 440752</t>
+          <t>394765; 470025</t>
         </is>
       </c>
     </row>
